--- a/artfynd/A 37862-2026 artfynd.xlsx
+++ b/artfynd/A 37862-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>518739</v>
+        <v>137387654</v>
       </c>
       <c r="B3" t="n">
-        <v>97785</v>
+        <v>96997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +812,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>500 m Ö Hallsjön (03F9e38), Bl</t>
+          <t>Långasjörundan, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522923</v>
+        <v>522799</v>
       </c>
       <c r="R3" t="n">
-        <v>6243545</v>
+        <v>6243805</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,17 +870,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-04-07</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-04-07</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>030594381 / FRUL TAM / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+          <t>Stora kuddar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,23 +889,14 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bergbrant /</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Gammal bok</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -909,23 +904,19 @@
           <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/518739</t>
+          <t>https://artportalen.se/Sighting/137387654</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>566714</v>
+        <v>518739</v>
       </c>
       <c r="B4" t="n">
-        <v>96437</v>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -997,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>030594381 / NECK COM / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+          <t>030594381 / FRUL TAM / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,16 +1028,16 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/566714</t>
+          <t>https://artportalen.se/Sighting/518739</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>639209</v>
+        <v>566714</v>
       </c>
       <c r="B5" t="n">
-        <v>96426</v>
+        <v>96437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1118,7 +1109,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>030594381 / ANTI CUR / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+          <t>030594381 / NECK COM / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,16 +1149,16 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/639209</t>
+          <t>https://artportalen.se/Sighting/566714</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>701319</v>
+        <v>137387510</v>
       </c>
       <c r="B6" t="n">
-        <v>96231</v>
+        <v>96726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,37 +1166,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>500 m Ö Hallsjön (03F9e38), Bl</t>
+          <t>Långasjörundan, Bl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522923</v>
+        <v>522725</v>
       </c>
       <c r="R6" t="n">
-        <v>6243545</v>
+        <v>6243922</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,17 +1224,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2004-04-07</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2004-04-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>030594381 / HOMA SER / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,38 +1238,964 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bergbrant /</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Gammal bok</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387510</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>639209</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>500 m Ö Hallsjön (03F9e38), Bl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>522923</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6243545</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2004-04-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2004-04-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>030594381 / ANTI CUR / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bergbrant /</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gammal bok</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Niklas Lönnell</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/639209</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137387546</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96715</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långasjörundan, Bl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>522684</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6243915</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387546</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>701319</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>500 m Ö Hallsjön (03F9e38), Bl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>522923</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6243545</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2004-04-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2004-04-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>030594381 / HOMA SER / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bergbrant /</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Gammal bok</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/701319</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137387424</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92185</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långasjörundan, Bl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>522824</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6243908</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387424</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137385841</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92842</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långasjörundan, Bl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>522911</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6243562</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Vid basen av gammal tall.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137385841</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137385860</v>
+      </c>
+      <c r="B12" t="n">
+        <v>81179</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långasjörundan, Bl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>522805</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6243886</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt på senvuxen gammal ek.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137385860</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137387443</v>
+      </c>
+      <c r="B13" t="n">
+        <v>81179</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långasjörundan, Bl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>522860</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6243891</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt på en bok och en senvuxen ek.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387443</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137387582</v>
+      </c>
+      <c r="B14" t="n">
+        <v>81179</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långasjörundan, Bl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>522691</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6243951</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387582</t>
         </is>
       </c>
     </row>
@@ -1290,6 +2206,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37862-2026 artfynd.xlsx
+++ b/artfynd/A 37862-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137387654</v>
       </c>
       <c r="B3" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>137387510</v>
       </c>
       <c r="B6" t="n">
-        <v>96726</v>
+        <v>96732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137387546</v>
       </c>
       <c r="B8" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>137387424</v>
       </c>
       <c r="B10" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137385841</v>
       </c>
       <c r="B11" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137385860</v>
       </c>
       <c r="B12" t="n">
-        <v>81179</v>
+        <v>81184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137387443</v>
       </c>
       <c r="B13" t="n">
-        <v>81179</v>
+        <v>81184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>137387582</v>
       </c>
       <c r="B14" t="n">
-        <v>81179</v>
+        <v>81184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37862-2026 artfynd.xlsx
+++ b/artfynd/A 37862-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137387654</v>
       </c>
       <c r="B3" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>137387510</v>
       </c>
       <c r="B6" t="n">
-        <v>96732</v>
+        <v>96744</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137387546</v>
       </c>
       <c r="B8" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>137387424</v>
       </c>
       <c r="B10" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137385841</v>
       </c>
       <c r="B11" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137385860</v>
       </c>
       <c r="B12" t="n">
-        <v>81184</v>
+        <v>81195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137387443</v>
       </c>
       <c r="B13" t="n">
-        <v>81184</v>
+        <v>81195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>137387582</v>
       </c>
       <c r="B14" t="n">
-        <v>81184</v>
+        <v>81195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37862-2026 artfynd.xlsx
+++ b/artfynd/A 37862-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137387654</v>
       </c>
       <c r="B3" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>137387510</v>
       </c>
       <c r="B6" t="n">
-        <v>96744</v>
+        <v>96745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137387546</v>
       </c>
       <c r="B8" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>137387424</v>
       </c>
       <c r="B10" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137385841</v>
       </c>
       <c r="B11" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137385860</v>
       </c>
       <c r="B12" t="n">
-        <v>81195</v>
+        <v>81196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137387443</v>
       </c>
       <c r="B13" t="n">
-        <v>81195</v>
+        <v>81196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>137387582</v>
       </c>
       <c r="B14" t="n">
-        <v>81195</v>
+        <v>81196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37862-2026 artfynd.xlsx
+++ b/artfynd/A 37862-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137387654</v>
       </c>
       <c r="B3" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>137387510</v>
       </c>
       <c r="B6" t="n">
-        <v>96745</v>
+        <v>96748</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137387546</v>
       </c>
       <c r="B8" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>137387424</v>
       </c>
       <c r="B10" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137385841</v>
       </c>
       <c r="B11" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137385860</v>
       </c>
       <c r="B12" t="n">
-        <v>81196</v>
+        <v>81198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137387443</v>
       </c>
       <c r="B13" t="n">
-        <v>81196</v>
+        <v>81198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>137387582</v>
       </c>
       <c r="B14" t="n">
-        <v>81196</v>
+        <v>81198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37862-2026 artfynd.xlsx
+++ b/artfynd/A 37862-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137387654</v>
       </c>
       <c r="B3" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>137387510</v>
       </c>
       <c r="B6" t="n">
-        <v>96748</v>
+        <v>96752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137387546</v>
       </c>
       <c r="B8" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>137387424</v>
       </c>
       <c r="B10" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137385841</v>
       </c>
       <c r="B11" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137385860</v>
       </c>
       <c r="B12" t="n">
-        <v>81198</v>
+        <v>81202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137387443</v>
       </c>
       <c r="B13" t="n">
-        <v>81198</v>
+        <v>81202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>137387582</v>
       </c>
       <c r="B14" t="n">
-        <v>81198</v>
+        <v>81202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
